--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>137204969</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137204970</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137204972</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>137204975</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137204977</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>137204979</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137204980</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137204982</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>137204988</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137204992</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>137205000</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>137205002</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>137205005</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>137205006</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>137205010</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>137205011</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>137205012</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>137205014</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>137205015</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>137205030</v>
       </c>
       <c r="B39" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>137204969</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137204970</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137204972</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>137204975</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137204977</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>137204979</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137204980</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137204982</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>137204988</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137204992</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>137205000</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>137205002</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>137205005</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>137205006</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>137205010</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>137205011</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>137205012</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>137205014</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>137205015</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>137205030</v>
       </c>
       <c r="B39" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -2873,11 +2873,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -2995,11 +2991,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -3117,11 +3109,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -3239,11 +3227,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -3361,11 +3345,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -3600,11 +3580,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -3839,11 +3815,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -3961,11 +3933,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4083,11 +4051,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4205,11 +4169,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4327,11 +4287,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4449,11 +4405,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4571,11 +4523,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4693,11 +4641,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -4932,11 +4876,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>
@@ -5054,11 +4994,7 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svinkilen, Jmt</t>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>137204969</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137204970</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>137204972</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>137204975</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>137204977</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>137204979</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>137204980</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137204982</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>137204988</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>137204992</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>137205000</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137205002</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137205005</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137205006</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137205010</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>137205011</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>137205012</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>137205014</v>
       </c>
       <c r="B37" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>137205015</v>
       </c>
       <c r="B38" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>137205030</v>
       </c>
       <c r="B39" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>137204969</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137204970</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>137204972</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>137204975</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>137204977</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>137204979</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>137204980</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137204982</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>137204988</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>137204992</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>137205000</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137205002</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137205005</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137205006</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137205010</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>137205011</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>137205012</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>137205014</v>
       </c>
       <c r="B37" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>137205015</v>
       </c>
       <c r="B38" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>137205030</v>
       </c>
       <c r="B39" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>137204969</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>137204970</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>137204972</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>137204975</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>137204977</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>137204979</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>137204980</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>137204982</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>137204988</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>137204992</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>137205000</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>137205002</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137205005</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137205006</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137205010</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>137205011</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>137205012</v>
       </c>
       <c r="B36" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>137205014</v>
       </c>
       <c r="B37" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>137205015</v>
       </c>
       <c r="B38" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>137205030</v>
       </c>
       <c r="B39" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 36253-2026 artfynd.xlsx
+++ b/artfynd/A 36253-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137205018</v>
       </c>
       <c r="B2" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137205022</v>
       </c>
       <c r="B3" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137204984</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137204998</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137205025</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137205016</v>
       </c>
       <c r="B7" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137204993</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137205023</v>
       </c>
       <c r="B9" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137204983</v>
       </c>
       <c r="B10" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137204974</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137204985</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137204990</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137205004</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137205007</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137205017</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137205029</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>137205032</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137205033</v>
       </c>
       <c r="B19" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
